--- a/jpcore-r4/develop/CodeSystem-jp-dental-bodysitestatus-cs.xlsx
+++ b/jpcore-r4/develop/CodeSystem-jp-dental-bodysitestatus-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31</t>
+    <t>2024-11-18</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/CodeSystem-jp-dental-bodysitestatus-cs.xlsx
+++ b/jpcore-r4/develop/CodeSystem-jp-dental-bodysitestatus-cs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.3.0-dev</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-18</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/CodeSystem-jp-dental-bodysitestatus-cs.xlsx
+++ b/jpcore-r4/develop/CodeSystem-jp-dental-bodysitestatus-cs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="43">
   <si>
     <t>Property</t>
   </si>
@@ -126,7 +126,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>8</t>
+    <t>1</t>
   </si>
   <si>
     <t>Level</t>
@@ -141,55 +141,7 @@
     <t>Definition</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>TB-3-1</t>
-  </si>
-  <si>
-    <t>部（部を示す場合に使用）</t>
-  </si>
-  <si>
-    <t>TB-3-3</t>
-  </si>
-  <si>
-    <t>支台歯</t>
-  </si>
-  <si>
-    <t>TB-3-4</t>
-  </si>
-  <si>
-    <t>分割抜歯支台（根）</t>
-  </si>
-  <si>
-    <t>TB-3-5</t>
-  </si>
-  <si>
-    <t>便宜抜髄支台歯</t>
-  </si>
-  <si>
-    <t>TB-3-6</t>
-  </si>
-  <si>
-    <t>残根</t>
-  </si>
-  <si>
-    <t>TB-3-7</t>
-  </si>
-  <si>
-    <t>部インプラント</t>
-  </si>
-  <si>
-    <t>TB-3-8</t>
-  </si>
-  <si>
-    <t>部近心隙</t>
-  </si>
-  <si>
-    <t>TB-3-9</t>
-  </si>
-  <si>
-    <t>近心位に存在</t>
+    <t>0</t>
   </si>
 </sst>
 </file>
@@ -501,7 +453,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -520,99 +472,15 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>42</v>
       </c>
-      <c r="B2" t="s" s="2">
-        <v>43</v>
-      </c>
       <c r="C2" t="s" s="2">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D2" s="2"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="C3" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="D3" s="2"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="C4" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="D4" s="2"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="C5" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="D5" s="2"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>51</v>
-      </c>
-      <c r="C6" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>53</v>
-      </c>
-      <c r="C7" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="D7" s="2"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="C8" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="D8" s="2"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="C9" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="D9" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/jpcore-r4/develop/CodeSystem-jp-dental-bodysitestatus-cs.xlsx
+++ b/jpcore-r4/develop/CodeSystem-jp-dental-bodysitestatus-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30</t>
+    <t>2025-07-04</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/CodeSystem-jp-dental-bodysitestatus-cs.xlsx
+++ b/jpcore-r4/develop/CodeSystem-jp-dental-bodysitestatus-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/CodeSystem-jp-dental-bodysitestatus-cs.xlsx
+++ b/jpcore-r4/develop/CodeSystem-jp-dental-bodysitestatus-cs.xlsx
@@ -93,7 +93,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright Japan Dental Association 日本歯科医師会 &amp; FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan Dental Association 日本歯科医師会 &amp; FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>Case Sensitive</t>
